--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486784_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486784_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.416600000000001</v>
+        <v>6.7204</v>
       </c>
       <c r="E2" t="n">
-        <v>6.7201</v>
+        <v>5.2722</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6965</v>
+        <v>1.4482</v>
       </c>
       <c r="G2" t="n">
         <v>2.4271</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>3.6959</v>
+        <v>1.9997</v>
       </c>
       <c r="T2" t="n">
-        <v>3.1437</v>
+        <v>1.6958</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5522</v>
+        <v>0.3039</v>
       </c>
       <c r="V2" t="n">
         <v>0.9421</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.292</v>
+        <v>6.4907</v>
       </c>
       <c r="E3" t="n">
         <v>5.3495</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9425</v>
+        <v>1.1412</v>
       </c>
       <c r="G3" t="n">
         <v>4.7353</v>
@@ -688,13 +688,13 @@
         <v>1.5446</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2977</v>
+        <v>0.4964</v>
       </c>
       <c r="T3" t="n">
         <v>0.2756</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0222</v>
+        <v>0.2208</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. FORTES SILVA</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.253</v>
+        <v>4.8052</v>
       </c>
       <c r="E4" t="n">
-        <v>5.3909</v>
+        <v>1.0465</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1379</v>
+        <v>3.7586</v>
       </c>
       <c r="G4" t="n">
-        <v>2.2517</v>
+        <v>2.6769</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4417</v>
+        <v>1.2618</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1899</v>
+        <v>1.4152</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9911</v>
+        <v>1.2921</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7876</v>
+        <v>0.4353</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2035</v>
+        <v>0.8568</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.7393</v>
+        <v>1.3848</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3459</v>
+        <v>0.8264</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3934</v>
+        <v>0.5583</v>
       </c>
       <c r="P4" t="n">
         <v>0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>2.7031</v>
       </c>
       <c r="S4" t="n">
-        <v>0.673</v>
+        <v>0.4138</v>
       </c>
       <c r="T4" t="n">
-        <v>0.9099</v>
+        <v>0.7857</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2368</v>
+        <v>-0.3719</v>
       </c>
       <c r="V4" t="n">
-        <v>1.5559</v>
+        <v>0.9421</v>
       </c>
       <c r="W4" t="n">
-        <v>2.4554</v>
+        <v>0.8995</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8995</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>A. FORTES SILVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.5419</v>
+        <v>4.7111</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0429</v>
+        <v>4.8738</v>
       </c>
       <c r="F5" t="n">
-        <v>3.5848</v>
+        <v>-0.1627</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6769</v>
+        <v>2.2517</v>
       </c>
       <c r="H5" t="n">
-        <v>1.2618</v>
+        <v>2.4417</v>
       </c>
       <c r="I5" t="n">
-        <v>1.4152</v>
+        <v>-0.1899</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2921</v>
+        <v>2.9911</v>
       </c>
       <c r="K5" t="n">
-        <v>0.4353</v>
+        <v>2.7876</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8568</v>
+        <v>0.2035</v>
       </c>
       <c r="M5" t="n">
-        <v>1.3848</v>
+        <v>-0.7393</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8264</v>
+        <v>-0.3459</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5583</v>
+        <v>-0.3934</v>
       </c>
       <c r="P5" t="n">
         <v>0.7723</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7031</v>
+        <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8494</v>
+        <v>0.1311</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3037</v>
+        <v>0.3927</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.5457</v>
+        <v>-0.2616</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9421</v>
+        <v>1.5559</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8995</v>
+        <v>2.4554</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0426</v>
+        <v>-0.8995</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.199</v>
+        <v>3.3977</v>
       </c>
       <c r="E6" t="n">
         <v>5.0177</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.8187</v>
+        <v>-1.62</v>
       </c>
       <c r="G6" t="n">
         <v>3.5481</v>
@@ -922,13 +922,13 @@
         <v>0.1931</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3806</v>
+        <v>0.5792</v>
       </c>
       <c r="T6" t="n">
         <v>0.7997</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4191</v>
+        <v>-0.2205</v>
       </c>
       <c r="V6" t="n">
         <v>0.0426</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.9221</v>
+        <v>3.3811</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1206</v>
+        <v>2.0514</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8015</v>
+        <v>1.3297</v>
       </c>
       <c r="G7" t="n">
         <v>1.1436</v>
@@ -1000,13 +1000,13 @@
         <v>2.3169</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.121</v>
+        <v>0.338</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5518999999999999</v>
+        <v>0.3789</v>
       </c>
       <c r="U7" t="n">
-        <v>0.431</v>
+        <v>-0.0409</v>
       </c>
       <c r="V7" t="n">
         <v>1.5133</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.7663</v>
+        <v>2.0283</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3683</v>
+        <v>0.6304</v>
       </c>
       <c r="F8" t="n">
         <v>1.398</v>
@@ -1078,10 +1078,10 @@
         <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7723</v>
+        <v>1.0343</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6617</v>
+        <v>0.9237</v>
       </c>
       <c r="U8" t="n">
         <v>0.1106</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.4149</v>
+        <v>0.7171999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.159</v>
+        <v>-0.6132</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2559</v>
+        <v>1.3304</v>
       </c>
       <c r="G9" t="n">
         <v>0.3726</v>
@@ -1156,13 +1156,13 @@
         <v>1.1585</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8147</v>
+        <v>1.117</v>
       </c>
       <c r="T9" t="n">
-        <v>1.7924</v>
+        <v>1.0202</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0223</v>
+        <v>0.09669999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5833</v>
+        <v>-0.0358</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6907</v>
+        <v>-0.1184</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1075</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5667</v>
@@ -1234,13 +1234,13 @@
         <v>0.1931</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2096</v>
+        <v>0.3378</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0553</v>
+        <v>0.517</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1543</v>
+        <v>-0.1792</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1735</v>
+        <v>-0.8343</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1928</v>
+        <v>-0.7792</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0193</v>
+        <v>-0.0552</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2894</v>
@@ -1312,13 +1312,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1159</v>
+        <v>0.4551</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1654</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0495</v>
+        <v>-0.124</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.3951</v>
+        <v>-2.0157</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4743</v>
+        <v>0.8537</v>
       </c>
       <c r="F12" t="n">
         <v>-2.8694</v>
@@ -1390,10 +1390,10 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>0.8274</v>
+        <v>0.2068</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3788</v>
+        <v>0.7583</v>
       </c>
       <c r="U12" t="n">
         <v>-0.5515</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.1874</v>
+        <v>-4.6232</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6607</v>
+        <v>-3.2952</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.5267</v>
+        <v>-1.328</v>
       </c>
       <c r="G13" t="n">
         <v>-2.5927</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.5021</v>
+        <v>0.062</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1927</v>
+        <v>0.5582</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6948</v>
+        <v>-0.4962</v>
       </c>
       <c r="V13" t="n">
         <v>-1.5133</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>24.4665</v>
+        <v>24.7427</v>
       </c>
       <c r="E14" t="n">
-        <v>20.0133</v>
+        <v>20.2892</v>
       </c>
       <c r="F14" t="n">
-        <v>4.453299999999999</v>
+        <v>4.453399999999999</v>
       </c>
       <c r="G14" t="n">
         <v>14.2423</v>
@@ -1546,13 +1546,13 @@
         <v>14.4808</v>
       </c>
       <c r="S14" t="n">
-        <v>6.895399999999999</v>
+        <v>7.171200000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>8.409000000000001</v>
+        <v>8.684899999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5134</v>
+        <v>-1.5138</v>
       </c>
       <c r="V14" t="n">
         <v>1.398200000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2108</v>
+        <v>2.5392</v>
       </c>
       <c r="E15" t="n">
-        <v>5.2748</v>
+        <v>4.5508</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.064</v>
+        <v>-2.0117</v>
       </c>
       <c r="G15" t="n">
         <v>-0.0433</v>
@@ -1624,13 +1624,13 @@
         <v>2.3169</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8716</v>
+        <v>0.1999</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1027</v>
+        <v>0.3787</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2311</v>
+        <v>-0.1788</v>
       </c>
       <c r="V15" t="n">
         <v>0.06560000000000001</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. CAMPOS RODRÍGUEZ</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.878</v>
+        <v>1.4325</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6156</v>
+        <v>1.6717</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.7376</v>
+        <v>-0.2392</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0484</v>
+        <v>2.5874</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.3178</v>
+        <v>2.1714</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3662</v>
+        <v>0.416</v>
       </c>
       <c r="J16" t="n">
-        <v>1.7256</v>
+        <v>3.2375</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7996</v>
+        <v>1.4832</v>
       </c>
       <c r="L16" t="n">
-        <v>2.5252</v>
+        <v>1.7543</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.6772</v>
+        <v>-0.6501</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4818</v>
+        <v>0.6882</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.159</v>
+        <v>-1.3384</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5792</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q16" t="n">
         <v>-1.9308</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3515</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.761</v>
+        <v>-0.8343</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.6347</v>
+        <v>0.365</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1263</v>
+        <v>-1.1993</v>
       </c>
       <c r="V16" t="n">
-        <v>2.1698</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="W16" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2856</v>
+        <v>0.06560000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>G. CAMPOS RODRÍGUEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5067</v>
+        <v>1.1909</v>
       </c>
       <c r="E17" t="n">
-        <v>2.2824</v>
+        <v>1.9258</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.7757</v>
+        <v>-0.7349</v>
       </c>
       <c r="G17" t="n">
-        <v>0.627</v>
+        <v>0.0484</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7031</v>
+        <v>-0.3178</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0761</v>
+        <v>0.3662</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0139</v>
+        <v>1.7256</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0139</v>
+        <v>-0.7996</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.5252</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3869</v>
+        <v>-1.6772</v>
       </c>
       <c r="N17" t="n">
-        <v>0.6892</v>
+        <v>0.4818</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.0761</v>
+        <v>-2.159</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R17" t="n">
-        <v>0.1931</v>
+        <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0277</v>
+        <v>-0.4481</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2685</v>
+        <v>-0.3244</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2962</v>
+        <v>-0.1237</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2856</v>
+        <v>2.1698</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.4554</v>
       </c>
       <c r="X17" t="n">
         <v>-0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1848</v>
+        <v>0.4895</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2951</v>
+        <v>0.4964</v>
       </c>
       <c r="G18" t="n">
         <v>0.8962</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7115</v>
+        <v>-0.4068</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1104</v>
+        <v>-0.0069</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6011</v>
+        <v>-0.3998</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.11</v>
+        <v>0.2172</v>
       </c>
       <c r="E19" t="n">
-        <v>1.3615</v>
+        <v>1.455</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2515</v>
+        <v>-1.2378</v>
       </c>
       <c r="G19" t="n">
-        <v>2.5874</v>
+        <v>0.627</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1714</v>
+        <v>1.7031</v>
       </c>
       <c r="I19" t="n">
-        <v>0.416</v>
+        <v>-1.0761</v>
       </c>
       <c r="J19" t="n">
-        <v>3.2375</v>
+        <v>1.0139</v>
       </c>
       <c r="K19" t="n">
-        <v>1.4832</v>
+        <v>1.0139</v>
       </c>
       <c r="L19" t="n">
-        <v>1.7543</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6501</v>
+        <v>-0.3869</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6882</v>
+        <v>0.6892</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3384</v>
+        <v>-1.0761</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.1569</v>
+        <v>-0.3172</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0547</v>
+        <v>0.4411</v>
       </c>
       <c r="U19" t="n">
-        <v>-2.2116</v>
+        <v>-0.7583</v>
       </c>
       <c r="V19" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2856</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.14</v>
+        <v>-0.3527</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.8626</v>
+        <v>-0.5524</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.2774</v>
+        <v>0.1997</v>
       </c>
       <c r="G20" t="n">
         <v>-0.0975</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4286</v>
+        <v>-0.6413</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2759</v>
+        <v>0.0344</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1527</v>
+        <v>-0.6756</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.5323</v>
+        <v>-5.9144</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.9652</v>
+        <v>-3.7583</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5671</v>
+        <v>-2.1561</v>
       </c>
       <c r="G21" t="n">
         <v>-4.1706</v>
@@ -2092,13 +2092,13 @@
         <v>1.3515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.5005</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7725</v>
+        <v>-0.5657</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.728</v>
+        <v>-0.3169</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2473</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.8237</v>
+        <v>-6.7589</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.3375</v>
+        <v>-2.6478</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.4862</v>
+        <v>-4.1111</v>
       </c>
       <c r="G22" t="n">
         <v>-4.993</v>
@@ -2170,13 +2170,13 @@
         <v>0.7723</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2039</v>
+        <v>0.2687</v>
       </c>
       <c r="T22" t="n">
-        <v>1.1029</v>
+        <v>0.7927</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8991</v>
+        <v>-0.5239</v>
       </c>
       <c r="V22" t="n">
         <v>-1.8415</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. GANDARA MARTIN</t>
+          <t>E. GONZALEZ CAMEJO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.9423</v>
+        <v>-6.8676</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.408</v>
+        <v>-3.8902</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.5344</v>
+        <v>-2.9775</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.5849</v>
+        <v>-6.5119</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3382</v>
+        <v>-3.0124</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9231</v>
+        <v>-3.4995</v>
       </c>
       <c r="J23" t="n">
-        <v>1.6925</v>
+        <v>-2.779</v>
       </c>
       <c r="K23" t="n">
-        <v>1.6495</v>
+        <v>-1.5628</v>
       </c>
       <c r="L23" t="n">
-        <v>0.043</v>
+        <v>-1.2162</v>
       </c>
       <c r="M23" t="n">
-        <v>-4.2774</v>
+        <v>-3.7329</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3113</v>
+        <v>-1.4495</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.9661</v>
+        <v>-2.2833</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.7031</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q23" t="n">
-        <v>-4.827</v>
+        <v>-3.8616</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1239</v>
+        <v>2.51</v>
       </c>
       <c r="S23" t="n">
-        <v>0.1215</v>
+        <v>-0.4553</v>
       </c>
       <c r="T23" t="n">
-        <v>0.0547</v>
+        <v>0.1373</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0668</v>
+        <v>-0.5926</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.7759</v>
+        <v>1.4511</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.3282</v>
+        <v>2.6131</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.4477</v>
+        <v>-1.162</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>E. GONZALEZ CAMEJO</t>
+          <t>E. GANDARA MARTIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-7.9185</v>
+        <v>-6.9949</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3039</v>
+        <v>-3.2011</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.6146</v>
+        <v>-3.7938</v>
       </c>
       <c r="G24" t="n">
-        <v>-6.5119</v>
+        <v>-2.5849</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.0124</v>
+        <v>0.3382</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.4995</v>
+        <v>-2.9231</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.779</v>
+        <v>1.6925</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5628</v>
+        <v>1.6495</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.2162</v>
+        <v>0.043</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.7329</v>
+        <v>-4.2774</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.4495</v>
+        <v>-1.3113</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.2833</v>
+        <v>-2.9661</v>
       </c>
       <c r="P24" t="n">
-        <v>-1.3515</v>
+        <v>-2.7031</v>
       </c>
       <c r="Q24" t="n">
-        <v>-3.8616</v>
+        <v>-4.827</v>
       </c>
       <c r="R24" t="n">
-        <v>2.51</v>
+        <v>2.1239</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.5061</v>
+        <v>0.0689</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.2764</v>
+        <v>0.2616</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.2297</v>
+        <v>-0.1926</v>
       </c>
       <c r="V24" t="n">
-        <v>1.4511</v>
+        <v>-1.7759</v>
       </c>
       <c r="W24" t="n">
-        <v>2.6131</v>
+        <v>-0.3282</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.162</v>
+        <v>-1.4477</v>
       </c>
     </row>
     <row r="25">
@@ -2359,25 +2359,25 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-24.4665</v>
+        <v>-21.0192</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.453299999999999</v>
+        <v>-4.4534</v>
       </c>
       <c r="F25" t="n">
-        <v>-20.0134</v>
+        <v>-16.566</v>
       </c>
       <c r="G25" t="n">
         <v>-14.2422</v>
       </c>
       <c r="H25" t="n">
-        <v>-9.999999999976694e-05</v>
+        <v>-9.999999999982245e-05</v>
       </c>
       <c r="I25" t="n">
         <v>-14.2423</v>
       </c>
       <c r="J25" t="n">
-        <v>2.631099999999998</v>
+        <v>2.631099999999999</v>
       </c>
       <c r="K25" t="n">
         <v>1.3875</v>
@@ -2404,22 +2404,22 @@
         <v>12.55</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.895299999999999</v>
+        <v>-3.4481</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5136</v>
+        <v>1.5138</v>
       </c>
       <c r="U25" t="n">
-        <v>-8.409000000000001</v>
+        <v>-4.9615</v>
       </c>
       <c r="V25" t="n">
         <v>-1.3982</v>
       </c>
       <c r="W25" t="n">
-        <v>5.8827</v>
+        <v>5.882700000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>-7.280900000000001</v>
+        <v>-7.2809</v>
       </c>
     </row>
   </sheetData>
